--- a/Practical5.xlsx
+++ b/Practical5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Vhx\Academics\BIDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CFADB74-B0CA-4D86-AF05-4AD78D6BE5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B302BF6C-F8FB-4A7F-AD2E-0C898816DCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD9FFA61-F3EB-4CBF-8248-CD7AE7919A43}"/>
   </bookViews>
@@ -435,7 +435,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -443,23 +443,23 @@
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <f>C5</f>
-        <v>20</v>
-      </c>
-      <c r="F2">
+        <v>200</v>
+      </c>
+      <c r="H2">
         <v>25</v>
-      </c>
-      <c r="G2">
-        <v>30</v>
-      </c>
-      <c r="H2">
-        <v>35</v>
       </c>
       <c r="I2">
         <v>30</v>
       </c>
       <c r="J2">
+        <v>45</v>
+      </c>
+      <c r="K2">
+        <v>30</v>
+      </c>
+      <c r="L2">
         <v>24</v>
       </c>
     </row>
@@ -468,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>4</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>10</v>
       </c>
-      <c r="F3">
-        <f t="dataTable" ref="F3:J8" dt2D="1" dtr="1" r1="C4" r2="C3"/>
+      <c r="H3">
+        <f t="dataTable" ref="H3:L8" dt2D="1" dtr="1" r1="C4" r2="C3"/>
         <v>250</v>
-      </c>
-      <c r="G3">
-        <v>300</v>
-      </c>
-      <c r="H3">
-        <v>350</v>
       </c>
       <c r="I3">
         <v>300</v>
       </c>
       <c r="J3">
+        <v>450</v>
+      </c>
+      <c r="K3">
+        <v>300</v>
+      </c>
+      <c r="L3">
         <v>240</v>
       </c>
     </row>
@@ -500,22 +500,22 @@
       <c r="C4">
         <v>20</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>15</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>375</v>
-      </c>
-      <c r="G4">
-        <v>450</v>
-      </c>
-      <c r="H4">
-        <v>525</v>
       </c>
       <c r="I4">
         <v>450</v>
       </c>
       <c r="J4">
+        <v>675</v>
+      </c>
+      <c r="K4">
+        <v>450</v>
+      </c>
+      <c r="L4">
         <v>360</v>
       </c>
     </row>
@@ -525,84 +525,84 @@
       </c>
       <c r="C5">
         <f>C3*C4</f>
-        <v>20</v>
-      </c>
-      <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="G5">
         <v>12</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>300</v>
-      </c>
-      <c r="G5">
-        <v>360</v>
-      </c>
-      <c r="H5">
-        <v>420</v>
       </c>
       <c r="I5">
         <v>360</v>
       </c>
       <c r="J5">
+        <v>540</v>
+      </c>
+      <c r="K5">
+        <v>360</v>
+      </c>
+      <c r="L5">
         <v>288</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="E6">
+      <c r="G6">
         <v>20</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>500</v>
-      </c>
-      <c r="G6">
-        <v>600</v>
-      </c>
-      <c r="H6">
-        <v>700</v>
       </c>
       <c r="I6">
         <v>600</v>
       </c>
       <c r="J6">
+        <v>900</v>
+      </c>
+      <c r="K6">
+        <v>600</v>
+      </c>
+      <c r="L6">
         <v>480</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="E7">
+      <c r="G7">
         <v>18</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>450</v>
-      </c>
-      <c r="G7">
-        <v>540</v>
-      </c>
-      <c r="H7">
-        <v>630</v>
       </c>
       <c r="I7">
         <v>540</v>
       </c>
       <c r="J7">
+        <v>810</v>
+      </c>
+      <c r="K7">
+        <v>540</v>
+      </c>
+      <c r="L7">
         <v>432</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="E8">
+      <c r="G8">
         <v>25</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>625</v>
-      </c>
-      <c r="G8">
-        <v>750</v>
-      </c>
-      <c r="H8">
-        <v>875</v>
       </c>
       <c r="I8">
         <v>750</v>
       </c>
       <c r="J8">
+        <v>1125</v>
+      </c>
+      <c r="K8">
+        <v>750</v>
+      </c>
+      <c r="L8">
         <v>600</v>
       </c>
     </row>
@@ -612,6 +612,12 @@
       </c>
     </row>
   </sheetData>
+  <scenarios current="0" show="0">
+    <scenario name="Base Price and qty" locked="1" count="2" user="Vignesh" comment="Created by Vignesh on 12-03-2026">
+      <inputCells r="C3" val="10"/>
+      <inputCells r="C4" val="20"/>
+    </scenario>
+  </scenarios>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>